--- a/stories/arbres/TREE-VIV-003.xlsx
+++ b/stories/arbres/TREE-VIV-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est dans la chambre, avec maman. La gamelle du chat est vide. Nino touche le bord, tout doux. Maman dit : on remplit l'eau avec un adulte. On est doux. Maman verse l'eau. Nino tient le bol, doux. Le chat vient. Nino caresse, doux, avec maman. On prend soin avec un adulte. On est doux.</t>
+          <t>Nino est dans la chambre, avec maman. La gamelle du chat est vide. Nino touche le bord, tout doux. On remplit l'eau avec un adulte. On est doux. Maman verse l'eau. Nino tient le bol, doux. Le chat vient. Nino caresse, doux, avec maman. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est dans la chambre, avec maman. La gamelle du chat est vide. Nino touche le bord, tout doux.
+maman|On remplit l'eau avec un adulte. On est doux. Maman verse l'eau.
+narrateur|Nino tient le bol, doux. Le chat vient. Nino caresse, doux, avec maman. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino prend le ballon rouge, tout doux. Le chat regarde. Maman dit : on est doux. L'eau, c'est avec un adulte. Nino pose le ballon. Nino reste près de maman. On prend soin avec un adulte. On est doux.</t>
+          <t>Nino prend le ballon rouge, tout doux. Le chat regarde. On est doux. L'eau, c'est avec un adulte. Nino pose le ballon. Nino reste près de maman. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge, tout doux. Le chat regarde.
+maman|On est doux. L'eau, c'est avec un adulte.
+narrateur|Nino pose le ballon. Nino reste près de maman. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On remplit l'eau. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a rempli l'eau avec un adulte. Nino a été doux. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2231,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2400,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Tom. Un pain croustille. Nino dit bonjour à Tom, tout doux. Maman rappelle : l'eau, avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2591,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La lumière est claire. On chante un petit air. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On compte jusqu'à trois. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un chat miaule une fois. On montre du doigt. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Léa. La terre est un peu humide. Léa parle bas. Nino caresse l'air, doux. On prend soin avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Les chaussures font toc toc. On range la chaise. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Les chaussures font toc toc. On range la chaise. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Les chaussures font toc toc. On range la chaise. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La couverture est douce. On range un objet. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Une cloche tinte au loin. On se tient la main. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Sami. Un rire court, tout petit. Sami sourit. Nino montre la gamelle. Avec un adulte. Doux. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5312,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le bois sent le chaud. On dit merci. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On souffle doucement. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon sent la fleur. On écoute jusqu'au bout. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6481,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nino pose le seau bleu près de la gamelle. Maman verse un peu d'eau. Avec un adulte. Nino est doux. Le chat boit. Nino ne touche pas le museau trop fort. Doux. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6662,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On caresse le chat. Comment ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6835,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Doux. Avec maman. Nino a pris soin, avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6841,6 +7028,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7005,6 +7197,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Tom. Les chaussures font toc toc. Tom attend. Nino reste doux. Maman est l'adulte, tout près. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7388,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7215,7 +7417,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Le tissu est tout doux. On attend son tour. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Le tissu est tout doux. On attend son tour. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7353,6 +7555,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le tissu est tout doux. On attend son tour. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une cuillère tinte. On sourit ensemble. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le sable est tiède. On pose les pieds par terre. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8187,7 +8420,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers Léa. Une feuille tourne et tombe. Léa écoute. Maman dit : doux, avec un adulte. Nino répète. On prend soin avec un adulte. On est doux.</t>
+          <t>Nino va vers Léa. Une feuille tourne et tombe. Léa écoute. Doux, avec un adulte. Nino répète. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8325,6 +8558,13 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Léa. Une feuille tourne et tombe. Léa écoute.
+maman|Doux, avec un adulte.
+narrateur|Nino répète. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8751,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8918,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un rire court, tout petit. On parle tout bas. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9085,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9252,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On range les jouets. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9419,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9586,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On s'assoit un moment. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9753,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9920,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Sami. Le savon glisse. Sami tend le doudou. Nino le prend, doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10111,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9855,7 +10140,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Un pigeon roucoule. On respire, un, deux. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Un pigeon roucoule. On respire, un, deux. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9993,6 +10278,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un pigeon roucoule. On respire, un, deux. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10446,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10613,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On referme le sac. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10780,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10947,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On essuie une miette. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11114,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11143,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nino pose le doudou sur le lit. Le chat frotte sa patte. Maman dit : doux. On prend soin avec un adulte. Nino caresse le dos, tout léger. Maman est là. On prend soin avec un adulte. On est doux.</t>
+          <t>Nino pose le doudou sur le lit. Le chat frotte sa patte. Doux. On prend soin avec un adulte. Nino caresse le dos, tout léger. Maman est là. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11281,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nino pose le doudou sur le lit. Le chat frotte sa patte.
+maman|Doux. On prend soin avec un adulte.
+narrateur|Nino caresse le dos, tout léger. Maman est là. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|La gamelle. On fait ça avec qui ?</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La gamelle est pleine. Avec un adulte. Nino reste doux. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11501,6 +11834,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11665,6 +12003,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Tom. Des miettes dorment sur la table. Nino et Tom regardent le chat. On est doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11851,6 +12194,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12013,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La corde du sac est rêche. On met le doudou près. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12175,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12337,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On lace les chaussures. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12499,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12661,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un ruisseau chante. On met le manteau. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12823,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12985,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Léa. Ça sent le pain tiède. Léa chuchote. Nino pose une main légère. Doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13171,6 +13554,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13195,7 +13583,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. La laine gratte un peu. On boit une gorgée. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. La laine gratte un peu. On boit une gorgée. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13333,6 +13721,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La laine gratte un peu. On boit une gorgée. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13889,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14056,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Un pain croustille. On feuillette le livre. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14223,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13981,6 +14390,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon glisse. On referme le livre. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14557,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14305,6 +14724,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers Sami. La fenêtre vibre un peu. Sami s'assoit. Maman verse encore un peu. Avec un adulte. Doux. On prend soin avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14491,6 +14915,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14653,6 +15082,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Une plume vole. On pose le ballon. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14815,6 +15249,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14977,6 +15416,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le banc est lisse. On secoue le sable. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15139,6 +15583,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15301,6 +15750,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un grelot sonne. On caresse le tissu. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15463,6 +15917,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15481,7 +15940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15512,6 +15971,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-003.xlsx
+++ b/stories/arbres/TREE-VIV-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Nino tient le bol, doux. Le chat vient. Nino caresse, doux, avec maman. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Nino pose le ballon. Nino reste près de maman. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|On remplit l'eau. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Nino a rempli l'eau avec un adulte. Nino a été doux. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
           <t>narrateur|Nino va vers Tom. Un pain croustille. Nino dit bonjour à Tom, tout doux. Maman rappelle : l'eau, avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2608,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2776,7 @@
           <t>narrateur|Voilà le matin. La lumière est claire. On chante un petit air. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3112,7 @@
           <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On compte jusqu'à trois. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
           <t>narrateur|Voilà le soir. Un chat miaule une fois. On montre du doigt. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Nino va vers Léa. La terre est un peu humide. Léa parle bas. Nino caresse l'air, doux. On prend soin avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Voilà après la sieste. La couverture est douce. On range un objet. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Voilà le soir. Une cloche tinte au loin. On se tient la main. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Nino va vers Sami. Un rire court, tout petit. Sami sourit. Nino montre la gamelle. Avec un adulte. Doux. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Voilà le matin. Le bois sent le chaud. On dit merci. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On souffle doucement. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Voilà le soir. Le savon sent la fleur. On écoute jusqu'au bout. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6486,6 +6521,7 @@
           <t>narrateur|Nino pose le seau bleu près de la gamelle. Maman verse un peu d'eau. Avec un adulte. Nino est doux. Le chat boit. Nino ne touche pas le museau trop fort. Doux. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6669,6 +6705,7 @@
           <t>narrateur|On caresse le chat. Comment ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6840,6 +6877,7 @@
           <t>narrateur|Doux. Avec maman. Nino a pris soin, avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7035,6 +7073,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7241,7 @@
           <t>narrateur|Nino va vers Tom. Les chaussures font toc toc. Tom attend. Nino reste doux. Maman est l'adulte, tout près. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7393,6 +7433,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Voilà après la sieste. Une cuillère tinte. On sourit ensemble. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Voilà le soir. Le sable est tiède. On pose les pieds par terre. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8565,6 +8612,7 @@
 narrateur|Nino répète. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8756,6 +8804,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8923,6 +8972,7 @@
           <t>narrateur|Voilà le matin. Un rire court, tout petit. On parle tout bas. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9090,6 +9140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9257,6 +9308,7 @@
           <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On range les jouets. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9424,6 +9476,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9591,6 +9644,7 @@
           <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On s'assoit un moment. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9758,6 +9812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9925,6 +9980,7 @@
           <t>narrateur|Nino va vers Sami. Le savon glisse. Sami tend le doudou. Nino le prend, doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10116,6 +10172,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10284,6 +10341,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10451,6 +10509,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10618,6 +10677,7 @@
           <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On referme le sac. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10785,6 +10845,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10952,6 +11013,7 @@
           <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On essuie une miette. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11119,6 +11181,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11288,6 +11351,7 @@
 narrateur|Nino caresse le dos, tout léger. Maman est là. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|La gamelle. On fait ça avec qui ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|La gamelle est pleine. Avec un adulte. Nino reste doux. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11841,6 +11907,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12008,6 +12075,7 @@
           <t>narrateur|Nino va vers Tom. Des miettes dorment sur la table. Nino et Tom regardent le chat. On est doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Voilà le matin. La corde du sac est rêche. On met le doudou près. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On lace les chaussures. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Voilà le soir. Un ruisseau chante. On met le manteau. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Nino va vers Léa. Ça sent le pain tiède. Léa chuchote. Nino pose une main légère. Doux. Avec un adulte. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13559,6 +13635,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13727,6 +13804,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13894,6 +13972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14061,6 +14140,7 @@
           <t>narrateur|Voilà après la sieste. Un pain croustille. On feuillette le livre. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14228,6 +14308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14395,6 +14476,7 @@
           <t>narrateur|Voilà le soir. Le savon glisse. On referme le livre. On a pris soin avec un adulte. On a été doux. L'adulte était là. On prend soin avec un adulte. On est doux. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14562,6 +14644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14729,6 +14812,7 @@
           <t>narrateur|Nino va vers Sami. La fenêtre vibre un peu. Sami s'assoit. Maman verse encore un peu. Avec un adulte. Doux. On prend soin avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14920,6 +15004,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15087,6 +15172,7 @@
           <t>narrateur|Voilà le matin. Une plume vole. On pose le ballon. On a pris soin avec un adulte. On a été doux. L'eau est pleine. On prend soin avec un adulte. On est doux. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15254,6 +15340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15421,6 +15508,7 @@
           <t>narrateur|Voilà après la sieste. Le banc est lisse. On secoue le sable. On a pris soin avec un adulte. On a été doux. La main était légère. On prend soin avec un adulte. On est doux. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15588,6 +15676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15755,6 +15844,7 @@
           <t>narrateur|Voilà le soir. Un grelot sonne. On caresse le tissu. On a pris soin avec un adulte. On a été doux. Le chat a bu. On prend soin avec un adulte. On est doux. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15922,6 +16012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15940,7 +16031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15978,6 +16069,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15992,7 +16097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16179,6 +16284,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
